--- a/TabelasDoRelatório.xlsx
+++ b/TabelasDoRelatório.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PoliQuant\Git\Pairs-TradingCode\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PoliQuant\Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42DB094-CBC7-4A63-9CD9-82A3B77FBD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D9B9B5-CA10-4D12-81A3-68F1B7793772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{66D57D90-870E-4A99-8C7C-D49F49113274}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>Empresas ativas até 2024-12-20</t>
   </si>
@@ -53,12 +53,6 @@
     <t>Resultado final</t>
   </si>
   <si>
-    <t>Lookback</t>
-  </si>
-  <si>
-    <t>Dinâmico (Halflife)</t>
-  </si>
-  <si>
     <t>entry_z</t>
   </si>
   <si>
@@ -138,6 +132,18 @@
   </si>
   <si>
     <t>MRVE3 / EZTC3</t>
+  </si>
+  <si>
+    <t>beta_min</t>
+  </si>
+  <si>
+    <t>beta_max</t>
+  </si>
+  <si>
+    <t>Parâmetro</t>
+  </si>
+  <si>
+    <t>Valor</t>
   </si>
 </sst>
 </file>
@@ -305,7 +311,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -314,22 +320,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -715,8 +721,8 @@
     <col min="3" max="3" width="20.5703125" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="11.140625" customWidth="1"/>
     <col min="13" max="13" width="2.85546875" customWidth="1"/>
@@ -732,25 +738,25 @@
         <v>1257</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M2" s="7">
         <v>8</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P2" s="7">
         <v>5</v>
@@ -764,25 +770,25 @@
         <v>1135</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J3" s="14">
         <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M3" s="7">
         <v>27</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P3" s="7">
         <v>6</v>
@@ -796,13 +802,13 @@
         <v>528</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="8">
         <v>0</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J4" s="14">
         <v>6</v>
@@ -818,13 +824,13 @@
         <v>474</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J5" s="14">
         <v>5</v>
@@ -839,32 +845,48 @@
       <c r="C6" s="6">
         <v>474</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="8">
+        <v>-0.70230000000000004</v>
+      </c>
       <c r="I6" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J6" s="14">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="8">
+        <v>4.8696999999999999</v>
+      </c>
       <c r="I7" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J7" s="14">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F8" s="1"/>
+      <c r="G8" s="8"/>
       <c r="I8" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J8" s="14">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F9" s="1"/>
+      <c r="G9" s="7"/>
       <c r="I9" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J9" s="14">
         <v>5</v>
@@ -872,7 +894,7 @@
     </row>
     <row r="10" spans="2:16" ht="28.5" x14ac:dyDescent="0.25">
       <c r="I10" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J10" s="14">
         <v>6</v>
@@ -880,7 +902,7 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="I11" s="15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J11" s="16">
         <v>57</v>
@@ -889,24 +911,24 @@
     <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="2:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D17" s="9">
         <v>9.8800000000000008</v>
@@ -917,10 +939,10 @@
     </row>
     <row r="18" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D18" s="9">
         <v>7.98</v>
@@ -931,10 +953,10 @@
     </row>
     <row r="19" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D19" s="9">
         <v>5.87</v>
@@ -946,24 +968,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D22" s="9">
         <v>4.79</v>
@@ -974,10 +996,10 @@
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D23" s="9">
         <v>4.37</v>
@@ -988,10 +1010,10 @@
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" s="9">
         <v>8.49</v>
